--- a/output/sliding_window_results_window_6.xlsx
+++ b/output/sliding_window_results_window_6.xlsx
@@ -460,16 +460,16 @@
         <v>19</v>
       </c>
       <c r="B2" t="n">
-        <v>30.95</v>
+        <v>40.1</v>
       </c>
       <c r="C2" t="n">
-        <v>28.94880888752401</v>
+        <v>41.96581708884483</v>
       </c>
       <c r="D2" t="n">
-        <v>-2.00119111247599</v>
+        <v>1.865817088844828</v>
       </c>
       <c r="E2" t="n">
-        <v>4.00476586865289</v>
+        <v>3.481273409025389</v>
       </c>
     </row>
     <row r="3">
@@ -477,16 +477,16 @@
         <v>18</v>
       </c>
       <c r="B3" t="n">
-        <v>31.38</v>
+        <v>41.5</v>
       </c>
       <c r="C3" t="n">
-        <v>29.71057783003733</v>
+        <v>41.711695471358</v>
       </c>
       <c r="D3" t="n">
-        <v>-1.669422169962672</v>
+        <v>0.2116954713579986</v>
       </c>
       <c r="E3" t="n">
-        <v>2.786970381562877</v>
+        <v>0.04481497259348521</v>
       </c>
     </row>
     <row r="4">
@@ -494,16 +494,16 @@
         <v>17</v>
       </c>
       <c r="B4" t="n">
-        <v>32.28</v>
+        <v>43.7</v>
       </c>
       <c r="C4" t="n">
-        <v>30.78345546244584</v>
+        <v>47.00649267126384</v>
       </c>
       <c r="D4" t="n">
-        <v>-1.496544537554165</v>
+        <v>3.30649267126384</v>
       </c>
       <c r="E4" t="n">
-        <v>2.239645552883209</v>
+        <v>10.93289378512148</v>
       </c>
     </row>
     <row r="5">
@@ -511,16 +511,16 @@
         <v>16</v>
       </c>
       <c r="B5" t="n">
-        <v>33.1</v>
+        <v>48.1</v>
       </c>
       <c r="C5" t="n">
-        <v>32.01972447248417</v>
+        <v>53.67965478183157</v>
       </c>
       <c r="D5" t="n">
-        <v>-1.08027552751583</v>
+        <v>5.579654781831564</v>
       </c>
       <c r="E5" t="n">
-        <v>1.166995215349606</v>
+        <v>31.13254748441584</v>
       </c>
     </row>
     <row r="6">
@@ -528,16 +528,16 @@
         <v>15</v>
       </c>
       <c r="B6" t="n">
-        <v>34.4</v>
+        <v>53</v>
       </c>
       <c r="C6" t="n">
-        <v>33.39122887585066</v>
+        <v>60.46953234507882</v>
       </c>
       <c r="D6" t="n">
-        <v>-1.008771124149341</v>
+        <v>7.469532345078818</v>
       </c>
       <c r="E6" t="n">
-        <v>1.017619180917525</v>
+        <v>55.79391345417866</v>
       </c>
     </row>
     <row r="7">
@@ -545,16 +545,16 @@
         <v>14</v>
       </c>
       <c r="B7" t="n">
-        <v>36.3</v>
+        <v>56.1</v>
       </c>
       <c r="C7" t="n">
-        <v>34.22165457885018</v>
+        <v>63.4057125300334</v>
       </c>
       <c r="D7" t="n">
-        <v>-2.07834542114982</v>
+        <v>7.305712530033396</v>
       </c>
       <c r="E7" t="n">
-        <v>4.319519689614421</v>
+        <v>53.37343557148697</v>
       </c>
     </row>
     <row r="8">
@@ -562,16 +562,16 @@
         <v>13</v>
       </c>
       <c r="B8" t="n">
-        <v>38.5</v>
+        <v>60</v>
       </c>
       <c r="C8" t="n">
-        <v>36.03681471918818</v>
+        <v>61.69497264564391</v>
       </c>
       <c r="D8" t="n">
-        <v>-2.463185280811821</v>
+        <v>1.694972645643908</v>
       </c>
       <c r="E8" t="n">
-        <v>6.06728172760801</v>
+        <v>2.872932269481109</v>
       </c>
     </row>
     <row r="9">
@@ -579,16 +579,16 @@
         <v>12</v>
       </c>
       <c r="B9" t="n">
-        <v>40.1</v>
+        <v>63.9</v>
       </c>
       <c r="C9" t="n">
-        <v>38.54186583503471</v>
+        <v>68.14176376957369</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.558134164965288</v>
+        <v>4.241763769573687</v>
       </c>
       <c r="E9" t="n">
-        <v>2.427782076032077</v>
+        <v>17.99255987686798</v>
       </c>
     </row>
     <row r="10">
@@ -596,16 +596,16 @@
         <v>11</v>
       </c>
       <c r="B10" t="n">
-        <v>41.5</v>
+        <v>70.59999999999999</v>
       </c>
       <c r="C10" t="n">
-        <v>39.5532811604554</v>
+        <v>72.75906081066678</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.946718839544602</v>
+        <v>2.159060810666787</v>
       </c>
       <c r="E10" t="n">
-        <v>3.78971424023788</v>
+        <v>4.661543584157124</v>
       </c>
     </row>
     <row r="11">
@@ -613,16 +613,16 @@
         <v>10</v>
       </c>
       <c r="B11" t="n">
-        <v>43.7</v>
+        <v>80.90000000000001</v>
       </c>
       <c r="C11" t="n">
-        <v>43.08141891598021</v>
+        <v>84.43893683999769</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.6185810840197945</v>
+        <v>3.538936839997689</v>
       </c>
       <c r="E11" t="n">
-        <v>0.3826425575071041</v>
+        <v>12.52407395749283</v>
       </c>
     </row>
     <row r="12">
@@ -630,16 +630,16 @@
         <v>9</v>
       </c>
       <c r="B12" t="n">
-        <v>48.1</v>
+        <v>89.09999999999999</v>
       </c>
       <c r="C12" t="n">
-        <v>44.3740341387837</v>
+        <v>86.24917119977155</v>
       </c>
       <c r="D12" t="n">
-        <v>-3.725965861216302</v>
+        <v>-2.850828800228442</v>
       </c>
       <c r="E12" t="n">
-        <v>13.88282159894934</v>
+        <v>8.127224848211936</v>
       </c>
     </row>
     <row r="13">
@@ -647,16 +647,16 @@
         <v>8</v>
       </c>
       <c r="B13" t="n">
-        <v>53</v>
+        <v>95</v>
       </c>
       <c r="C13" t="n">
-        <v>50.59095506823863</v>
+        <v>86.20267413907692</v>
       </c>
       <c r="D13" t="n">
-        <v>-2.409044931761372</v>
+        <v>-8.797325860923081</v>
       </c>
       <c r="E13" t="n">
-        <v>5.803497483245152</v>
+        <v>77.39294230326603</v>
       </c>
     </row>
     <row r="14">
@@ -664,16 +664,16 @@
         <v>7</v>
       </c>
       <c r="B14" t="n">
-        <v>56.1</v>
+        <v>98.8</v>
       </c>
       <c r="C14" t="n">
-        <v>53.90122652945816</v>
+        <v>99.27078128583433</v>
       </c>
       <c r="D14" t="n">
-        <v>-2.198773470541845</v>
+        <v>0.4707812858343345</v>
       </c>
       <c r="E14" t="n">
-        <v>4.834604774758628</v>
+        <v>0.2216350190918294</v>
       </c>
     </row>
     <row r="15">
@@ -681,16 +681,16 @@
         <v>6</v>
       </c>
       <c r="B15" t="n">
-        <v>60</v>
+        <v>103.3</v>
       </c>
       <c r="C15" t="n">
-        <v>58.43032535307836</v>
+        <v>99.0848327458443</v>
       </c>
       <c r="D15" t="n">
-        <v>-1.569674646921641</v>
+        <v>-4.215167254155702</v>
       </c>
       <c r="E15" t="n">
-        <v>2.463878497188578</v>
+        <v>17.76763498050652</v>
       </c>
     </row>
     <row r="16">
@@ -698,16 +698,16 @@
         <v>5</v>
       </c>
       <c r="B16" t="n">
-        <v>63.9</v>
+        <v>107</v>
       </c>
       <c r="C16" t="n">
-        <v>58.89387613612693</v>
+        <v>106.9674252458498</v>
       </c>
       <c r="D16" t="n">
-        <v>-5.006123863873071</v>
+        <v>-0.03257475415017552</v>
       </c>
       <c r="E16" t="n">
-        <v>25.06127614043945</v>
+        <v>0.001061114607944378</v>
       </c>
     </row>
     <row r="17">
@@ -715,16 +715,16 @@
         <v>4</v>
       </c>
       <c r="B17" t="n">
-        <v>70.59999999999999</v>
+        <v>108.7</v>
       </c>
       <c r="C17" t="n">
-        <v>67.55813908812617</v>
+        <v>118.6049624326626</v>
       </c>
       <c r="D17" t="n">
-        <v>-3.041860911873826</v>
+        <v>9.904962432662586</v>
       </c>
       <c r="E17" t="n">
-        <v>9.252917807185865</v>
+        <v>98.10828079245714</v>
       </c>
     </row>
     <row r="18">
@@ -732,16 +732,16 @@
         <v>3</v>
       </c>
       <c r="B18" t="n">
-        <v>80.90000000000001</v>
+        <v>112.7</v>
       </c>
       <c r="C18" t="n">
-        <v>76.7645357980953</v>
+        <v>119.2293366045231</v>
       </c>
       <c r="D18" t="n">
-        <v>-4.135464201904711</v>
+        <v>6.529336604523081</v>
       </c>
       <c r="E18" t="n">
-        <v>17.10206416523537</v>
+        <v>42.632236495165</v>
       </c>
     </row>
     <row r="19">
@@ -749,16 +749,16 @@
         <v>2</v>
       </c>
       <c r="B19" t="n">
-        <v>89.09999999999999</v>
+        <v>117.2</v>
       </c>
       <c r="C19" t="n">
-        <v>85.72078635250307</v>
+        <v>128.3559067244275</v>
       </c>
       <c r="D19" t="n">
-        <v>-3.379213647496925</v>
+        <v>11.15590672442754</v>
       </c>
       <c r="E19" t="n">
-        <v>11.41908487542947</v>
+        <v>124.4542548441276</v>
       </c>
     </row>
     <row r="20">
@@ -766,16 +766,16 @@
         <v>1</v>
       </c>
       <c r="B20" t="n">
-        <v>95</v>
+        <v>123.1</v>
       </c>
       <c r="C20" t="n">
-        <v>92.07083187560471</v>
+        <v>125.5792828778016</v>
       </c>
       <c r="D20" t="n">
-        <v>-2.929168124395289</v>
+        <v>2.479282877801566</v>
       </c>
       <c r="E20" t="n">
-        <v>8.580025900973418</v>
+        <v>6.146843588160015</v>
       </c>
     </row>
     <row r="21">
@@ -783,16 +783,16 @@
         <v>0</v>
       </c>
       <c r="B21" t="n">
-        <v>98.8</v>
+        <v>128.9</v>
       </c>
       <c r="C21" t="n">
-        <v>94.66706929610125</v>
+        <v>131.7345564269283</v>
       </c>
       <c r="D21" t="n">
-        <v>-4.132930703898751</v>
+        <v>2.834556426928344</v>
       </c>
       <c r="E21" t="n">
-        <v>17.08111620322902</v>
+        <v>8.034710137440783</v>
       </c>
     </row>
     <row r="22">
@@ -803,11 +803,11 @@
       </c>
       <c r="B22" t="inlineStr"/>
       <c r="C22" t="n">
-        <v>-48.44938962603305</v>
+        <v>54.85256863701257</v>
       </c>
       <c r="D22" t="inlineStr"/>
       <c r="E22" t="n">
-        <v>143.6842239369999</v>
+        <v>575.6968124878556</v>
       </c>
     </row>
     <row r="23">
@@ -820,7 +820,7 @@
       <c r="C23" t="inlineStr"/>
       <c r="D23" t="inlineStr"/>
       <c r="E23" t="n">
-        <v>7.184211196849995</v>
+        <v>28.78484062439278</v>
       </c>
     </row>
   </sheetData>
